--- a/Thesis Forecasting/outputs/rbfnn_forecast/Day_Ahead_24H_RBFNN_Forecast.xlsx
+++ b/Thesis Forecasting/outputs/rbfnn_forecast/Day_Ahead_24H_RBFNN_Forecast.xlsx
@@ -21,13 +21,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -451,139 +463,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit1_MW</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit2_MW</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit1_MW</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit2_MW</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit3_MW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit1_MW</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit2_MW</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit3_MW</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit1_MW</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit2_MW</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit1_MW</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit2_MW</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit3_MW</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit4_MW</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit5_MW</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit1_MW</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit2_MW</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus1_MW</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus2_MW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus4_MW</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus5_MW</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus6_MW</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus7_MW</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Total_Cascade_Generation_MW</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -698,10 +710,10 @@
         <v>48.09448391746024</v>
       </c>
       <c r="K3" t="n">
-        <v>21.30858265837536</v>
+        <v>21.30858265839634</v>
       </c>
       <c r="L3" t="n">
-        <v>21.28442961672615</v>
+        <v>21.2844296167471</v>
       </c>
       <c r="M3" t="n">
         <v>34.5</v>
@@ -734,7 +746,7 @@
         <v>140.6654424907493</v>
       </c>
       <c r="W3" t="n">
-        <v>42.59301227510151</v>
+        <v>42.59301227514344</v>
       </c>
       <c r="X3" t="n">
         <v>157.6367187498603</v>
@@ -743,11 +755,11 @@
         <v>42.287962115</v>
       </c>
       <c r="Z3" t="n">
-        <v>573.1394083563637</v>
+        <v>573.1394083564055</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -780,10 +792,10 @@
         <v>48.1076103174649</v>
       </c>
       <c r="K4" t="n">
-        <v>21.56941378424554</v>
+        <v>21.56941378426438</v>
       </c>
       <c r="L4" t="n">
-        <v>21.63242757951646</v>
+        <v>21.63242757953535</v>
       </c>
       <c r="M4" t="n">
         <v>34.5</v>
@@ -816,7 +828,7 @@
         <v>140.6655751622455</v>
       </c>
       <c r="W4" t="n">
-        <v>43.201841363762</v>
+        <v>43.20184136379973</v>
       </c>
       <c r="X4" t="n">
         <v>157.4643499997904</v>
@@ -825,11 +837,11 @@
         <v>42.13754530833798</v>
       </c>
       <c r="Z4" t="n">
-        <v>573.3664375402922</v>
+        <v>573.3664375403299</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,10 +874,10 @@
         <v>48.1108961523446</v>
       </c>
       <c r="K5" t="n">
-        <v>21.6058264236209</v>
+        <v>21.60582642365875</v>
       </c>
       <c r="L5" t="n">
-        <v>21.71025114908358</v>
+        <v>21.71025114912161</v>
       </c>
       <c r="M5" t="n">
         <v>34.5</v>
@@ -898,20 +910,20 @@
         <v>140.6514370326202</v>
       </c>
       <c r="W5" t="n">
-        <v>43.31607757270449</v>
+        <v>43.31607757278036</v>
       </c>
       <c r="X5" t="n">
-        <v>157.4030437497205</v>
+        <v>157.4030437497204</v>
       </c>
       <c r="Y5" t="n">
         <v>42.00115351208728</v>
       </c>
       <c r="Z5" t="n">
-        <v>573.1632135731491</v>
+        <v>573.1632135732248</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,13 +938,13 @@
         <v>29.62472397453831</v>
       </c>
       <c r="E6" t="n">
-        <v>40.42486858578125</v>
+        <v>40.42486858578127</v>
       </c>
       <c r="F6" t="n">
-        <v>37.46643926163906</v>
+        <v>37.46643926163907</v>
       </c>
       <c r="G6" t="n">
-        <v>51.59215586404451</v>
+        <v>51.59215586404453</v>
       </c>
       <c r="H6" t="n">
         <v>47.31712270000441</v>
@@ -944,10 +956,10 @@
         <v>48.12051141272349</v>
       </c>
       <c r="K6" t="n">
-        <v>21.92238841843827</v>
+        <v>21.92238841845143</v>
       </c>
       <c r="L6" t="n">
-        <v>22.05407316515818</v>
+        <v>22.05407316517141</v>
       </c>
       <c r="M6" t="n">
         <v>34.5</v>
@@ -974,13 +986,13 @@
         <v>60.16918400256112</v>
       </c>
       <c r="U6" t="n">
-        <v>129.4834637114648</v>
+        <v>129.4834637114649</v>
       </c>
       <c r="V6" t="n">
         <v>140.6769457779949</v>
       </c>
       <c r="W6" t="n">
-        <v>43.97646158359645</v>
+        <v>43.97646158362284</v>
       </c>
       <c r="X6" t="n">
         <v>157.2981749996506</v>
@@ -989,11 +1001,11 @@
         <v>42.16791298527419</v>
       </c>
       <c r="Z6" t="n">
-        <v>573.772143060542</v>
+        <v>573.7721430605684</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1008,28 +1020,28 @@
         <v>29.65533686365298</v>
       </c>
       <c r="E7" t="n">
-        <v>40.29538144327552</v>
+        <v>40.29538144327553</v>
       </c>
       <c r="F7" t="n">
-        <v>37.44942726045555</v>
+        <v>37.44942726045557</v>
       </c>
       <c r="G7" t="n">
-        <v>51.62443891214318</v>
+        <v>51.62443891214321</v>
       </c>
       <c r="H7" t="n">
-        <v>47.3175609782818</v>
+        <v>47.31756097828178</v>
       </c>
       <c r="I7" t="n">
-        <v>45.25556134568008</v>
+        <v>45.25556134568006</v>
       </c>
       <c r="J7" t="n">
-        <v>48.13374469940771</v>
+        <v>48.1337446994077</v>
       </c>
       <c r="K7" t="n">
-        <v>22.02301323370817</v>
+        <v>22.02301323372001</v>
       </c>
       <c r="L7" t="n">
-        <v>22.15616218606992</v>
+        <v>22.15616218608183</v>
       </c>
       <c r="M7" t="n">
         <v>34.5</v>
@@ -1059,10 +1071,10 @@
         <v>129.3692476158743</v>
       </c>
       <c r="V7" t="n">
-        <v>140.7068670233696</v>
+        <v>140.7068670233695</v>
       </c>
       <c r="W7" t="n">
-        <v>44.1791754197781</v>
+        <v>44.17917541980184</v>
       </c>
       <c r="X7" t="n">
         <v>157.0333062495807</v>
@@ -1071,11 +1083,11 @@
         <v>41.57438103748306</v>
       </c>
       <c r="Z7" t="n">
-        <v>573.0317573486468</v>
+        <v>573.0317573486706</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1090,28 +1102,28 @@
         <v>29.65501230904961</v>
       </c>
       <c r="E8" t="n">
-        <v>40.16550183406882</v>
+        <v>40.16550183406884</v>
       </c>
       <c r="F8" t="n">
-        <v>37.42407262222657</v>
+        <v>37.42407262222659</v>
       </c>
       <c r="G8" t="n">
-        <v>51.65185340646814</v>
+        <v>51.65185340646817</v>
       </c>
       <c r="H8" t="n">
-        <v>47.30570598961825</v>
+        <v>47.30570598961823</v>
       </c>
       <c r="I8" t="n">
-        <v>45.25608556216837</v>
+        <v>45.25608556216835</v>
       </c>
       <c r="J8" t="n">
-        <v>48.13258314307919</v>
+        <v>48.13258314307917</v>
       </c>
       <c r="K8" t="n">
-        <v>22.00549678427708</v>
+        <v>22.00549678428775</v>
       </c>
       <c r="L8" t="n">
-        <v>22.07524102113499</v>
+        <v>22.07524102114569</v>
       </c>
       <c r="M8" t="n">
         <v>34.5</v>
@@ -1138,13 +1150,13 @@
         <v>60.16837600256112</v>
       </c>
       <c r="U8" t="n">
-        <v>129.2414278627635</v>
+        <v>129.2414278627636</v>
       </c>
       <c r="V8" t="n">
         <v>140.6943746948658</v>
       </c>
       <c r="W8" t="n">
-        <v>44.08073780541208</v>
+        <v>44.08073780543344</v>
       </c>
       <c r="X8" t="n">
         <v>156.9018124995108</v>
@@ -1153,11 +1165,11 @@
         <v>40.03288138200903</v>
       </c>
       <c r="Z8" t="n">
-        <v>571.1196102471223</v>
+        <v>571.1196102471437</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1172,28 +1184,28 @@
         <v>29.65263083629384</v>
       </c>
       <c r="E9" t="n">
-        <v>40.05722979370528</v>
+        <v>40.0572297937053</v>
       </c>
       <c r="F9" t="n">
-        <v>37.40337401701331</v>
+        <v>37.40337401701332</v>
       </c>
       <c r="G9" t="n">
-        <v>51.63753589329114</v>
+        <v>51.63753589329116</v>
       </c>
       <c r="H9" t="n">
-        <v>47.26991451926948</v>
+        <v>47.26991451926946</v>
       </c>
       <c r="I9" t="n">
-        <v>45.23006751267872</v>
+        <v>45.2300675126787</v>
       </c>
       <c r="J9" t="n">
-        <v>48.10286704246</v>
+        <v>48.10286704245998</v>
       </c>
       <c r="K9" t="n">
-        <v>22.26214067532714</v>
+        <v>22.26214067533675</v>
       </c>
       <c r="L9" t="n">
-        <v>22.30986597989342</v>
+        <v>22.30986597990304</v>
       </c>
       <c r="M9" t="n">
         <v>34.5</v>
@@ -1220,13 +1232,13 @@
         <v>60.16797200256111</v>
       </c>
       <c r="U9" t="n">
-        <v>129.0981397040097</v>
+        <v>129.0981397040098</v>
       </c>
       <c r="V9" t="n">
-        <v>140.6028490744082</v>
+        <v>140.6028490744081</v>
       </c>
       <c r="W9" t="n">
-        <v>44.57200665522056</v>
+        <v>44.57200665523979</v>
       </c>
       <c r="X9" t="n">
         <v>156.7944749994409</v>
@@ -1235,11 +1247,11 @@
         <v>39.55916417470768</v>
       </c>
       <c r="Z9" t="n">
-        <v>570.7946066103481</v>
+        <v>570.7946066103674</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1254,28 +1266,28 @@
         <v>29.66457349398418</v>
       </c>
       <c r="E10" t="n">
-        <v>40.01052883064387</v>
+        <v>40.01052883064389</v>
       </c>
       <c r="F10" t="n">
-        <v>37.36099041335389</v>
+        <v>37.3609904133539</v>
       </c>
       <c r="G10" t="n">
-        <v>51.63159545987229</v>
+        <v>51.63159545987231</v>
       </c>
       <c r="H10" t="n">
-        <v>47.29110819431158</v>
+        <v>47.29110819431156</v>
       </c>
       <c r="I10" t="n">
-        <v>45.23863386078767</v>
+        <v>45.23863386078765</v>
       </c>
       <c r="J10" t="n">
-        <v>48.11998969080518</v>
+        <v>48.11998969080516</v>
       </c>
       <c r="K10" t="n">
-        <v>22.18473148764715</v>
+        <v>22.18473148765581</v>
       </c>
       <c r="L10" t="n">
-        <v>22.15940391380474</v>
+        <v>22.15940391381339</v>
       </c>
       <c r="M10" t="n">
         <v>34.5</v>
@@ -1302,13 +1314,13 @@
         <v>60.16756800256111</v>
       </c>
       <c r="U10" t="n">
-        <v>129.00311470387</v>
+        <v>129.0031147038701</v>
       </c>
       <c r="V10" t="n">
         <v>140.6497317459044</v>
       </c>
       <c r="W10" t="n">
-        <v>44.34413540145188</v>
+        <v>44.3441354014692</v>
       </c>
       <c r="X10" t="n">
         <v>157.082012499371</v>
@@ -1317,11 +1329,11 @@
         <v>40.19489335772493</v>
       </c>
       <c r="Z10" t="n">
-        <v>571.4414557108834</v>
+        <v>571.4414557109006</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1336,28 +1348,28 @@
         <v>29.67801296017533</v>
       </c>
       <c r="E11" t="n">
-        <v>39.95621769281914</v>
+        <v>39.95621769281916</v>
       </c>
       <c r="F11" t="n">
-        <v>37.30077636389905</v>
+        <v>37.30077636389908</v>
       </c>
       <c r="G11" t="n">
-        <v>51.58559564701218</v>
+        <v>51.58559564701221</v>
       </c>
       <c r="H11" t="n">
-        <v>47.2711005541078</v>
+        <v>47.27110055419783</v>
       </c>
       <c r="I11" t="n">
-        <v>45.20692119312959</v>
+        <v>45.20692119321568</v>
       </c>
       <c r="J11" t="n">
-        <v>48.08908480211784</v>
+        <v>48.08908480220942</v>
       </c>
       <c r="K11" t="n">
-        <v>21.83829382380848</v>
+        <v>21.83829382381628</v>
       </c>
       <c r="L11" t="n">
-        <v>21.78729703898829</v>
+        <v>21.78729703899607</v>
       </c>
       <c r="M11" t="n">
         <v>34.5</v>
@@ -1384,13 +1396,13 @@
         <v>60.16716400256111</v>
       </c>
       <c r="U11" t="n">
-        <v>128.8425897037304</v>
+        <v>128.8425897037305</v>
       </c>
       <c r="V11" t="n">
-        <v>140.5671065493552</v>
+        <v>140.5671065496229</v>
       </c>
       <c r="W11" t="n">
-        <v>43.62559086279676</v>
+        <v>43.62559086281234</v>
       </c>
       <c r="X11" t="n">
         <v>156.8941437493012</v>
@@ -1399,11 +1411,11 @@
         <v>40.51129539453316</v>
       </c>
       <c r="Z11" t="n">
-        <v>570.6078902622778</v>
+        <v>570.6078902625612</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,28 +1430,28 @@
         <v>29.68192958640483</v>
       </c>
       <c r="E12" t="n">
-        <v>39.91503220717159</v>
+        <v>39.91503220717161</v>
       </c>
       <c r="F12" t="n">
-        <v>37.26072161369993</v>
+        <v>37.26072161369994</v>
       </c>
       <c r="G12" t="n">
-        <v>51.53530901992612</v>
+        <v>51.53530901992615</v>
       </c>
       <c r="H12" t="n">
-        <v>47.28420973678661</v>
+        <v>47.28420973696669</v>
       </c>
       <c r="I12" t="n">
-        <v>45.21616809644095</v>
+        <v>45.21616809661316</v>
       </c>
       <c r="J12" t="n">
-        <v>48.094215581415</v>
+        <v>48.09421558159817</v>
       </c>
       <c r="K12" t="n">
-        <v>21.75380670094467</v>
+        <v>21.75380670097269</v>
       </c>
       <c r="L12" t="n">
-        <v>21.68175933597384</v>
+        <v>21.68175933600176</v>
       </c>
       <c r="M12" t="n">
         <v>34.5</v>
@@ -1466,13 +1478,13 @@
         <v>60.16676000256111</v>
       </c>
       <c r="U12" t="n">
-        <v>128.7110628407976</v>
+        <v>128.7110628407977</v>
       </c>
       <c r="V12" t="n">
-        <v>140.5945934146426</v>
+        <v>140.594593415178</v>
       </c>
       <c r="W12" t="n">
-        <v>43.43556603691852</v>
+        <v>43.43556603697444</v>
       </c>
       <c r="X12" t="n">
         <v>156.8256499992314</v>
@@ -1481,11 +1493,11 @@
         <v>40.69771863650655</v>
       </c>
       <c r="Z12" t="n">
-        <v>570.4313509306578</v>
+        <v>570.4313509312492</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1500,28 +1512,28 @@
         <v>29.69521576418174</v>
       </c>
       <c r="E13" t="n">
-        <v>39.87260963127866</v>
+        <v>39.87260963127868</v>
       </c>
       <c r="F13" t="n">
-        <v>37.22238276181514</v>
+        <v>37.22238276181515</v>
       </c>
       <c r="G13" t="n">
-        <v>51.46425044756419</v>
+        <v>51.46425044756421</v>
       </c>
       <c r="H13" t="n">
-        <v>47.29214424905378</v>
+        <v>47.29214424923389</v>
       </c>
       <c r="I13" t="n">
-        <v>45.22156828056663</v>
+        <v>45.22156828073884</v>
       </c>
       <c r="J13" t="n">
-        <v>48.08974274415108</v>
+        <v>48.08974274433422</v>
       </c>
       <c r="K13" t="n">
-        <v>21.76632782998013</v>
+        <v>21.76632783000534</v>
       </c>
       <c r="L13" t="n">
-        <v>21.693643812992</v>
+        <v>21.69364381301713</v>
       </c>
       <c r="M13" t="n">
         <v>34.5</v>
@@ -1530,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>47.75646328538919</v>
+        <v>47.75646328538913</v>
       </c>
       <c r="P13" t="n">
-        <v>24.56056796377237</v>
+        <v>24.56056796377234</v>
       </c>
       <c r="Q13" t="n">
         <v>50</v>
@@ -1551,10 +1563,10 @@
         <v>128.559242840658</v>
       </c>
       <c r="V13" t="n">
-        <v>140.6034552737715</v>
+        <v>140.603455274307</v>
       </c>
       <c r="W13" t="n">
-        <v>43.45997164297214</v>
+        <v>43.45997164302248</v>
       </c>
       <c r="X13" t="n">
         <v>156.8170312491615</v>
@@ -1563,11 +1575,11 @@
         <v>41.03774084103057</v>
       </c>
       <c r="Z13" t="n">
-        <v>570.6437978501548</v>
+        <v>570.6437978507405</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1582,28 +1594,28 @@
         <v>29.68986039782022</v>
       </c>
       <c r="E14" t="n">
-        <v>39.85085805004208</v>
+        <v>39.85085805004209</v>
       </c>
       <c r="F14" t="n">
-        <v>37.17688999482613</v>
+        <v>37.17688999482614</v>
       </c>
       <c r="G14" t="n">
-        <v>51.42603446030193</v>
+        <v>51.42603446030196</v>
       </c>
       <c r="H14" t="n">
-        <v>47.319371699765</v>
+        <v>47.31937169994512</v>
       </c>
       <c r="I14" t="n">
-        <v>45.24243257972429</v>
+        <v>45.24243257989652</v>
       </c>
       <c r="J14" t="n">
-        <v>48.10415865506821</v>
+        <v>48.10415865525133</v>
       </c>
       <c r="K14" t="n">
-        <v>21.42202667970038</v>
+        <v>21.42202667972307</v>
       </c>
       <c r="L14" t="n">
-        <v>21.34616665638494</v>
+        <v>21.34616665640755</v>
       </c>
       <c r="M14" t="n">
         <v>34.5</v>
@@ -1612,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>47.81577747126333</v>
+        <v>47.81577747126329</v>
       </c>
       <c r="P14" t="n">
-        <v>24.59107252782838</v>
+        <v>24.59107252782836</v>
       </c>
       <c r="Q14" t="n">
         <v>50</v>
@@ -1630,13 +1642,13 @@
         <v>60.1659520025611</v>
       </c>
       <c r="U14" t="n">
-        <v>128.4537825051701</v>
+        <v>128.4537825051702</v>
       </c>
       <c r="V14" t="n">
-        <v>140.6659629345575</v>
+        <v>140.665962935093</v>
       </c>
       <c r="W14" t="n">
-        <v>42.76819333608532</v>
+        <v>42.76819333613062</v>
       </c>
       <c r="X14" t="n">
         <v>156.9068499990917</v>
@@ -1645,11 +1657,11 @@
         <v>40.54250596487597</v>
       </c>
       <c r="Z14" t="n">
-        <v>569.5032467423417</v>
+        <v>569.5032467429226</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1664,28 +1676,28 @@
         <v>29.69057042419135</v>
       </c>
       <c r="E15" t="n">
-        <v>39.8123220051265</v>
+        <v>39.81232200512652</v>
       </c>
       <c r="F15" t="n">
-        <v>37.13467287719001</v>
+        <v>37.13467287719003</v>
       </c>
       <c r="G15" t="n">
-        <v>51.38113562485596</v>
+        <v>51.38113562485599</v>
       </c>
       <c r="H15" t="n">
-        <v>47.29346221332872</v>
+        <v>47.29346221350883</v>
       </c>
       <c r="I15" t="n">
-        <v>45.22600706176117</v>
+        <v>45.2260070619334</v>
       </c>
       <c r="J15" t="n">
-        <v>48.08314614493531</v>
+        <v>48.08314614511843</v>
       </c>
       <c r="K15" t="n">
-        <v>21.24927429250274</v>
+        <v>21.24927429252316</v>
       </c>
       <c r="L15" t="n">
-        <v>21.17767872953236</v>
+        <v>21.17767872955271</v>
       </c>
       <c r="M15" t="n">
         <v>34.5</v>
@@ -1694,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>47.73847628214889</v>
+        <v>47.73847628214885</v>
       </c>
       <c r="P15" t="n">
-        <v>24.55131746687297</v>
+        <v>24.55131746687295</v>
       </c>
       <c r="Q15" t="n">
         <v>50</v>
@@ -1715,23 +1727,23 @@
         <v>128.3281305071725</v>
       </c>
       <c r="V15" t="n">
-        <v>140.6026154200252</v>
+        <v>140.6026154205607</v>
       </c>
       <c r="W15" t="n">
-        <v>42.42695302203509</v>
+        <v>42.42695302207586</v>
       </c>
       <c r="X15" t="n">
-        <v>156.7897937490219</v>
+        <v>156.7897937490218</v>
       </c>
       <c r="Y15" t="n">
         <v>40.65537507014457</v>
       </c>
       <c r="Z15" t="n">
-        <v>568.9684157709603</v>
+        <v>568.9684157715366</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1746,28 +1758,28 @@
         <v>29.69483814412473</v>
       </c>
       <c r="E16" t="n">
-        <v>39.76004676756925</v>
+        <v>39.76004676756927</v>
       </c>
       <c r="F16" t="n">
-        <v>37.07902459537951</v>
+        <v>37.07902459537952</v>
       </c>
       <c r="G16" t="n">
-        <v>51.31782410783018</v>
+        <v>51.3178241078302</v>
       </c>
       <c r="H16" t="n">
-        <v>47.281908536151</v>
+        <v>47.28190853642115</v>
       </c>
       <c r="I16" t="n">
-        <v>45.22012435253496</v>
+        <v>45.22012435279333</v>
       </c>
       <c r="J16" t="n">
-        <v>48.08019439662655</v>
+        <v>48.08019439690126</v>
       </c>
       <c r="K16" t="n">
-        <v>21.20868923970156</v>
+        <v>21.20868923971994</v>
       </c>
       <c r="L16" t="n">
-        <v>21.13650621105453</v>
+        <v>21.13650621107285</v>
       </c>
       <c r="M16" t="n">
         <v>34.5</v>
@@ -1776,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>47.67838615387141</v>
+        <v>47.67838615387137</v>
       </c>
       <c r="P16" t="n">
-        <v>24.52041384508064</v>
+        <v>24.52041384508062</v>
       </c>
       <c r="Q16" t="n">
         <v>50</v>
@@ -1794,13 +1806,13 @@
         <v>60.16514400256109</v>
       </c>
       <c r="U16" t="n">
-        <v>128.1568954707789</v>
+        <v>128.156895470779</v>
       </c>
       <c r="V16" t="n">
-        <v>140.5822272853125</v>
+        <v>140.5822272861157</v>
       </c>
       <c r="W16" t="n">
-        <v>42.34519545075609</v>
+        <v>42.34519545079279</v>
       </c>
       <c r="X16" t="n">
         <v>156.698799998952</v>
@@ -1809,11 +1821,11 @@
         <v>40.39930505962288</v>
       </c>
       <c r="Z16" t="n">
-        <v>568.3475672679834</v>
+        <v>568.3475672688235</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1828,28 +1840,28 @@
         <v>29.70076798895276</v>
       </c>
       <c r="E17" t="n">
-        <v>39.71117130969873</v>
+        <v>39.71117130969875</v>
       </c>
       <c r="F17" t="n">
-        <v>37.06066031448209</v>
+        <v>37.06066031448211</v>
       </c>
       <c r="G17" t="n">
-        <v>51.26302522209808</v>
+        <v>51.26302522209809</v>
       </c>
       <c r="H17" t="n">
-        <v>47.28363844606273</v>
+        <v>47.28363844633288</v>
       </c>
       <c r="I17" t="n">
-        <v>45.22236598875588</v>
+        <v>45.22236598901424</v>
       </c>
       <c r="J17" t="n">
-        <v>48.08248051395745</v>
+        <v>48.08248051423216</v>
       </c>
       <c r="K17" t="n">
-        <v>21.07330594470873</v>
+        <v>21.07330594474626</v>
       </c>
       <c r="L17" t="n">
-        <v>21.00228819062475</v>
+        <v>21.00228819066216</v>
       </c>
       <c r="M17" t="n">
         <v>34.5</v>
@@ -1858,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>46.46606916094952</v>
+        <v>46.46606916094947</v>
       </c>
       <c r="P17" t="n">
-        <v>25.58198708793278</v>
+        <v>25.58198708793276</v>
       </c>
       <c r="Q17" t="n">
         <v>50</v>
@@ -1876,26 +1888,26 @@
         <v>60.16474000256109</v>
       </c>
       <c r="U17" t="n">
-        <v>128.0348568462789</v>
+        <v>128.034856846279</v>
       </c>
       <c r="V17" t="n">
-        <v>140.5884849487761</v>
+        <v>140.5884849495793</v>
       </c>
       <c r="W17" t="n">
-        <v>42.07559413533348</v>
+        <v>42.07559413540842</v>
       </c>
       <c r="X17" t="n">
-        <v>156.5480562488823</v>
+        <v>156.5480562488822</v>
       </c>
       <c r="Y17" t="n">
         <v>40.46715555067944</v>
       </c>
       <c r="Z17" t="n">
-        <v>567.8788877325112</v>
+        <v>567.8788877333894</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1910,28 +1922,28 @@
         <v>29.68890174308342</v>
       </c>
       <c r="E18" t="n">
-        <v>39.6672020463427</v>
+        <v>39.66720204634272</v>
       </c>
       <c r="F18" t="n">
-        <v>37.00884415149728</v>
+        <v>37.00884415149729</v>
       </c>
       <c r="G18" t="n">
-        <v>51.19019348590318</v>
+        <v>51.19019348590321</v>
       </c>
       <c r="H18" t="n">
-        <v>47.25829211076372</v>
+        <v>47.25829211103387</v>
       </c>
       <c r="I18" t="n">
-        <v>45.19745907108721</v>
+        <v>45.19745907134558</v>
       </c>
       <c r="J18" t="n">
-        <v>48.05394874248591</v>
+        <v>48.05394874276061</v>
       </c>
       <c r="K18" t="n">
-        <v>20.98923227572171</v>
+        <v>20.98923227575549</v>
       </c>
       <c r="L18" t="n">
-        <v>20.92746022721052</v>
+        <v>20.9274602272442</v>
       </c>
       <c r="M18" t="n">
         <v>34.5</v>
@@ -1940,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>42.99789272654868</v>
+        <v>42.99789272654864</v>
       </c>
       <c r="P18" t="n">
-        <v>29.0632947722637</v>
+        <v>29.06329477226368</v>
       </c>
       <c r="Q18" t="n">
         <v>50</v>
@@ -1961,23 +1973,23 @@
         <v>127.8662396837432</v>
       </c>
       <c r="V18" t="n">
-        <v>140.5096999243368</v>
+        <v>140.5096999251401</v>
       </c>
       <c r="W18" t="n">
-        <v>41.91669250293224</v>
+        <v>41.91669250299968</v>
       </c>
       <c r="X18" t="n">
-        <v>156.5611874988124</v>
+        <v>156.5611874988123</v>
       </c>
       <c r="Y18" t="n">
         <v>40.69119363879622</v>
       </c>
       <c r="Z18" t="n">
-        <v>567.7093492511819</v>
+        <v>567.7093492520526</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1992,28 +2004,28 @@
         <v>29.68169903841854</v>
       </c>
       <c r="E19" t="n">
-        <v>39.6572135815351</v>
+        <v>39.65721358153512</v>
       </c>
       <c r="F19" t="n">
         <v>36.97818246228152</v>
       </c>
       <c r="G19" t="n">
-        <v>51.1219922854423</v>
+        <v>51.12199228544232</v>
       </c>
       <c r="H19" t="n">
-        <v>47.25972839197104</v>
+        <v>47.25972839224116</v>
       </c>
       <c r="I19" t="n">
-        <v>45.20493970004487</v>
+        <v>45.20493970030324</v>
       </c>
       <c r="J19" t="n">
-        <v>48.06528304931353</v>
+        <v>48.06528304958826</v>
       </c>
       <c r="K19" t="n">
-        <v>21.07015786082399</v>
+        <v>21.07015786085439</v>
       </c>
       <c r="L19" t="n">
-        <v>21.00150323916418</v>
+        <v>21.00150323919448</v>
       </c>
       <c r="M19" t="n">
         <v>34.5</v>
@@ -2022,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>41.75481252879587</v>
+        <v>41.75481252879582</v>
       </c>
       <c r="P19" t="n">
-        <v>30.2729437199466</v>
+        <v>30.27294371994658</v>
       </c>
       <c r="Q19" t="n">
         <v>50</v>
@@ -2040,26 +2052,26 @@
         <v>60.16393200256108</v>
       </c>
       <c r="U19" t="n">
-        <v>127.7573883292589</v>
+        <v>127.757388329259</v>
       </c>
       <c r="V19" t="n">
-        <v>140.5299511413294</v>
+        <v>140.5299511421327</v>
       </c>
       <c r="W19" t="n">
-        <v>42.07166109998817</v>
+        <v>42.07166110004887</v>
       </c>
       <c r="X19" t="n">
-        <v>156.5277562487425</v>
+        <v>156.5277562487424</v>
       </c>
       <c r="Y19" t="n">
         <v>41.02224584297679</v>
       </c>
       <c r="Z19" t="n">
-        <v>568.0729346648568</v>
+        <v>568.0729346657207</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,28 +2086,28 @@
         <v>29.69965695086476</v>
       </c>
       <c r="E20" t="n">
-        <v>39.53960225988595</v>
+        <v>39.53960225988596</v>
       </c>
       <c r="F20" t="n">
         <v>37.08396730447944</v>
       </c>
       <c r="G20" t="n">
-        <v>51.00816676261182</v>
+        <v>51.00816676261184</v>
       </c>
       <c r="H20" t="n">
-        <v>47.29212656227842</v>
+        <v>47.29212656254852</v>
       </c>
       <c r="I20" t="n">
-        <v>45.23942284138849</v>
+        <v>45.23942284164687</v>
       </c>
       <c r="J20" t="n">
-        <v>48.10265939737751</v>
+        <v>48.10265939765225</v>
       </c>
       <c r="K20" t="n">
-        <v>20.80759460267835</v>
+        <v>20.8075946027057</v>
       </c>
       <c r="L20" t="n">
-        <v>20.73950041024159</v>
+        <v>20.73950041026885</v>
       </c>
       <c r="M20" t="n">
         <v>34.5</v>
@@ -2104,10 +2116,10 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>42.35759264422445</v>
+        <v>42.3575926442244</v>
       </c>
       <c r="P20" t="n">
-        <v>29.81704485444802</v>
+        <v>29.81704485444801</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2125,23 +2137,23 @@
         <v>127.6317363269772</v>
       </c>
       <c r="V20" t="n">
-        <v>140.6342088010444</v>
+        <v>140.6342088018476</v>
       </c>
       <c r="W20" t="n">
-        <v>41.54709501291994</v>
+        <v>41.54709501297455</v>
       </c>
       <c r="X20" t="n">
-        <v>156.6746374986725</v>
+        <v>156.6746374986724</v>
       </c>
       <c r="Y20" t="n">
         <v>41.13381683788893</v>
       </c>
       <c r="Z20" t="n">
-        <v>567.7850224800641</v>
+        <v>567.7850224809218</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2162,22 +2174,22 @@
         <v>37.21644985193731</v>
       </c>
       <c r="G21" t="n">
-        <v>50.85133031932155</v>
+        <v>50.85133031932158</v>
       </c>
       <c r="H21" t="n">
-        <v>47.27796127612471</v>
+        <v>47.2779612763948</v>
       </c>
       <c r="I21" t="n">
-        <v>45.22821593725673</v>
+        <v>45.22821593751512</v>
       </c>
       <c r="J21" t="n">
-        <v>48.09216486838044</v>
+        <v>48.09216486865519</v>
       </c>
       <c r="K21" t="n">
-        <v>20.75129399145033</v>
+        <v>20.75129399147494</v>
       </c>
       <c r="L21" t="n">
-        <v>20.67909025403876</v>
+        <v>20.6790902540633</v>
       </c>
       <c r="M21" t="n">
         <v>34.5</v>
@@ -2186,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>42.94342468632592</v>
+        <v>42.94342468632588</v>
       </c>
       <c r="P21" t="n">
-        <v>29.49334406227658</v>
+        <v>29.49334406227657</v>
       </c>
       <c r="Q21" t="n">
         <v>50</v>
@@ -2207,23 +2219,23 @@
         <v>127.4697165738665</v>
       </c>
       <c r="V21" t="n">
-        <v>140.5983420817619</v>
+        <v>140.5983420825651</v>
       </c>
       <c r="W21" t="n">
-        <v>41.43038424548909</v>
+        <v>41.43038424553824</v>
       </c>
       <c r="X21" t="n">
-        <v>156.9367687486025</v>
+        <v>156.9367687486024</v>
       </c>
       <c r="Y21" t="n">
         <v>41.44906807749382</v>
       </c>
       <c r="Z21" t="n">
-        <v>568.0474037297749</v>
+        <v>568.0474037306273</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2244,22 +2256,22 @@
         <v>37.26981706086575</v>
       </c>
       <c r="G22" t="n">
-        <v>50.74523188243453</v>
+        <v>50.74523188243455</v>
       </c>
       <c r="H22" t="n">
-        <v>47.29424250176737</v>
+        <v>47.29424250203745</v>
       </c>
       <c r="I22" t="n">
-        <v>45.24855979048173</v>
+        <v>45.24855979074014</v>
       </c>
       <c r="J22" t="n">
-        <v>48.11642307344327</v>
+        <v>48.11642307371805</v>
       </c>
       <c r="K22" t="n">
-        <v>20.84878419538621</v>
+        <v>20.84878419542936</v>
       </c>
       <c r="L22" t="n">
-        <v>20.76640124584328</v>
+        <v>20.76640124588627</v>
       </c>
       <c r="M22" t="n">
         <v>34.5</v>
@@ -2268,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>43.31639195947218</v>
+        <v>43.31639195947213</v>
       </c>
       <c r="P22" t="n">
-        <v>29.13669553906051</v>
+        <v>29.1366955390605</v>
       </c>
       <c r="Q22" t="n">
         <v>50</v>
@@ -2289,23 +2301,23 @@
         <v>127.3294742785544</v>
       </c>
       <c r="V22" t="n">
-        <v>140.6592253656924</v>
+        <v>140.6592253664956</v>
       </c>
       <c r="W22" t="n">
-        <v>41.61518544122949</v>
+        <v>41.61518544131563</v>
       </c>
       <c r="X22" t="n">
-        <v>156.9530874985327</v>
+        <v>156.9530874985326</v>
       </c>
       <c r="Y22" t="n">
         <v>41.19477287254907</v>
       </c>
       <c r="Z22" t="n">
-        <v>567.9144654591191</v>
+        <v>567.9144654600085</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2320,28 +2332,28 @@
         <v>29.68142595966556</v>
       </c>
       <c r="E23" t="n">
-        <v>39.26019938454956</v>
+        <v>39.26019938521054</v>
       </c>
       <c r="F23" t="n">
-        <v>37.28989204604783</v>
+        <v>37.28989204667565</v>
       </c>
       <c r="G23" t="n">
-        <v>50.68018283924918</v>
+        <v>50.68018284010245</v>
       </c>
       <c r="H23" t="n">
-        <v>47.24689137595065</v>
+        <v>47.2468913762207</v>
       </c>
       <c r="I23" t="n">
-        <v>45.2087922736099</v>
+        <v>45.2087922738683</v>
       </c>
       <c r="J23" t="n">
-        <v>48.07775670695464</v>
+        <v>48.07775670722943</v>
       </c>
       <c r="K23" t="n">
-        <v>20.39078765947263</v>
+        <v>20.39078765951136</v>
       </c>
       <c r="L23" t="n">
-        <v>20.41312816997853</v>
+        <v>20.41312817001731</v>
       </c>
       <c r="M23" t="n">
         <v>34.5</v>
@@ -2350,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>43.58916934152595</v>
+        <v>43.58916934152588</v>
       </c>
       <c r="P23" t="n">
-        <v>28.82011190693676</v>
+        <v>28.82011190693675</v>
       </c>
       <c r="Q23" t="n">
         <v>50</v>
@@ -2368,26 +2380,26 @@
         <v>60.16231600256107</v>
       </c>
       <c r="U23" t="n">
-        <v>127.2302742698466</v>
+        <v>127.2302742719886</v>
       </c>
       <c r="V23" t="n">
-        <v>140.5334403565152</v>
+        <v>140.5334403573185</v>
       </c>
       <c r="W23" t="n">
-        <v>40.80391582945116</v>
+        <v>40.80391582952868</v>
       </c>
       <c r="X23" t="n">
-        <v>156.9092812484627</v>
+        <v>156.9092812484626</v>
       </c>
       <c r="Y23" t="n">
         <v>40.65347444166672</v>
       </c>
       <c r="Z23" t="n">
-        <v>566.2927021485034</v>
+        <v>566.2927021515262</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2402,28 +2414,28 @@
         <v>29.67518248431647</v>
       </c>
       <c r="E24" t="n">
-        <v>39.21199731105483</v>
+        <v>39.21199731237642</v>
       </c>
       <c r="F24" t="n">
-        <v>37.27455706559903</v>
+        <v>37.27455706685532</v>
       </c>
       <c r="G24" t="n">
-        <v>50.62330011866158</v>
+        <v>50.62330012036778</v>
       </c>
       <c r="H24" t="n">
-        <v>47.2606454402401</v>
+        <v>47.26064544060017</v>
       </c>
       <c r="I24" t="n">
-        <v>45.22376140969176</v>
+        <v>45.22376141003631</v>
       </c>
       <c r="J24" t="n">
-        <v>48.09457974419308</v>
+        <v>48.0945797445595</v>
       </c>
       <c r="K24" t="n">
-        <v>20.83871024417667</v>
+        <v>20.83871024423242</v>
       </c>
       <c r="L24" t="n">
-        <v>20.9106708684488</v>
+        <v>20.91067086850474</v>
       </c>
       <c r="M24" t="n">
         <v>34.5</v>
@@ -2432,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>43.87543841527626</v>
+        <v>43.87543841527616</v>
       </c>
       <c r="P24" t="n">
-        <v>28.59922408311664</v>
+        <v>28.5992240831166</v>
       </c>
       <c r="Q24" t="n">
         <v>50</v>
@@ -2450,26 +2462,26 @@
         <v>60.16191200256107</v>
       </c>
       <c r="U24" t="n">
-        <v>127.1098544953154</v>
+        <v>127.1098544995995</v>
       </c>
       <c r="V24" t="n">
-        <v>140.578986594125</v>
+        <v>140.578986595196</v>
       </c>
       <c r="W24" t="n">
-        <v>41.74938111262547</v>
+        <v>41.74938111273715</v>
       </c>
       <c r="X24" t="n">
-        <v>156.9746624983929</v>
+        <v>156.9746624983928</v>
       </c>
       <c r="Y24" t="n">
         <v>40.99600577541671</v>
       </c>
       <c r="Z24" t="n">
-        <v>567.5708024784366</v>
+        <v>567.5708024839032</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,28 +2496,28 @@
         <v>29.68182505482505</v>
       </c>
       <c r="E25" t="n">
-        <v>39.15619496617838</v>
+        <v>39.15619496816019</v>
       </c>
       <c r="F25" t="n">
-        <v>37.23900829847959</v>
+        <v>37.23900830036438</v>
       </c>
       <c r="G25" t="n">
-        <v>50.57054992107822</v>
+        <v>50.57054992363776</v>
       </c>
       <c r="H25" t="n">
-        <v>47.26351565096715</v>
+        <v>47.2635156513272</v>
       </c>
       <c r="I25" t="n">
-        <v>45.22925163077012</v>
+        <v>45.22925163111468</v>
       </c>
       <c r="J25" t="n">
-        <v>48.09640928152235</v>
+        <v>48.09640928188875</v>
       </c>
       <c r="K25" t="n">
-        <v>20.84513417925982</v>
+        <v>20.84513417930996</v>
       </c>
       <c r="L25" t="n">
-        <v>20.94238418374449</v>
+        <v>20.94238418379486</v>
       </c>
       <c r="M25" t="n">
         <v>34.5</v>
@@ -2514,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>43.94654586240668</v>
+        <v>43.94654586240662</v>
       </c>
       <c r="P25" t="n">
-        <v>28.27181038591632</v>
+        <v>28.2718103859163</v>
       </c>
       <c r="Q25" t="n">
         <v>50</v>
@@ -2532,22 +2544,22 @@
         <v>60.16150800256106</v>
       </c>
       <c r="U25" t="n">
-        <v>126.9657531857362</v>
+        <v>126.9657531921623</v>
       </c>
       <c r="V25" t="n">
-        <v>140.5891765632596</v>
+        <v>140.5891765643306</v>
       </c>
       <c r="W25" t="n">
-        <v>41.78751836300431</v>
+        <v>41.78751836310482</v>
       </c>
       <c r="X25" t="n">
-        <v>156.718356248323</v>
+        <v>156.7183562483229</v>
       </c>
       <c r="Y25" t="n">
         <v>41.19300990910419</v>
       </c>
       <c r="Z25" t="n">
-        <v>567.4153222719883</v>
+        <v>567.4153222795859</v>
       </c>
     </row>
   </sheetData>
